--- a/erp-server/erp-server-plm/src/main/resources/excel/scheduleTask.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/scheduleTask.xlsx
@@ -38,7 +38,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>任务排期状态</t>
+    <t>任务状态</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
